--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,302 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>196600</v>
+      </c>
+      <c r="E8" s="3">
         <v>180000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>189700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>184000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>184100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>187300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>191800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>203300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>213300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>195100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>176600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>160400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>153500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>140500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>123300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>133400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>113300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>101700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>91500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>81700</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E9" s="3">
         <v>18700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>16300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16700</v>
-      </c>
-      <c r="G9" s="3">
-        <v>17400</v>
       </c>
       <c r="H9" s="3">
         <v>17400</v>
       </c>
       <c r="I9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="J9" s="3">
         <v>18000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>181400</v>
+      </c>
+      <c r="E10" s="3">
         <v>161300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>173400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>167300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>166700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>169900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>173800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>191000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>199400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>183800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>165500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>150000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>144300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>133000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>116500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>127400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>108700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>98300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>88400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>78800</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E12" s="3">
         <v>39600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>32900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>36800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>35900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>35400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>35000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>35100</v>
       </c>
       <c r="L12" s="3">
         <v>35100</v>
       </c>
       <c r="M12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="N12" s="3">
         <v>29600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5600</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,37 +1121,40 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>2400</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-8500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>18700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1143,11 +1162,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1155,12 +1174,12 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>4900</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1170,73 +1189,79 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E15" s="3">
         <v>33000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>15500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2600</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>214900</v>
+      </c>
+      <c r="E17" s="3">
         <v>220500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>171400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>174500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>182400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>203000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>195800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>183600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>201500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>188100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>177000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>165400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>453000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>202100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>81600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>89700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>82400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>63900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>53700</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-40500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-299500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-61600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>41700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>43700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>30900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>37800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>38000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>28000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,35 +1444,36 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E20" s="3">
         <v>8600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1451,122 +1484,128 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>-2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>42200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>31700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>22700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>22400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-295000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>46300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>48100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>44000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E22" s="3">
         <v>14700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>5900</v>
       </c>
       <c r="K22" s="3">
         <v>5900</v>
@@ -1581,164 +1620,173 @@
         <v>5900</v>
       </c>
       <c r="O22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="P22" s="3">
         <v>6200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13400</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-46600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>12100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-22300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-305600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-67900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>35000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>35100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>17900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>25300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>25000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14700</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-8100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-46700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>19500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-8700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>45800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-37300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-12600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-38500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>58800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-41700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-39900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>31100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-298300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>27300</v>
       </c>
       <c r="R26" s="3">
         <v>27300</v>
       </c>
       <c r="S26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="T26" s="3">
         <v>15200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>11600</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-38500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>58800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-39900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>31100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-298300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>27300</v>
       </c>
       <c r="R27" s="3">
         <v>27300</v>
       </c>
       <c r="S27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="T27" s="3">
         <v>15200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11600</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,35 +2258,38 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2231,99 +2300,105 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-38500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>58800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-41700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-39900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>31100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-298300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>27300</v>
       </c>
       <c r="R33" s="3">
         <v>27300</v>
       </c>
       <c r="S33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="T33" s="3">
         <v>15200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11600</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-38500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>58800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-41700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-39900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>31100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-298300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>27300</v>
       </c>
       <c r="R35" s="3">
         <v>27300</v>
       </c>
       <c r="S35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="T35" s="3">
         <v>15200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11600</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,56 +2657,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>672300</v>
+      </c>
+      <c r="E41" s="3">
         <v>794900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>762000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>761100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>757200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>728800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>730500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>845400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>941100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>912000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>894700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>990500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>968700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1075000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>126600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2637,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2702,56 +2791,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E43" s="3">
         <v>124600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>123400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>116400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>121700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>124300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>143200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>129100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>126400</v>
       </c>
       <c r="L43" s="3">
         <v>126400</v>
       </c>
       <c r="M43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="N43" s="3">
         <v>166800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>115800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>92300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>58800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2767,8 +2859,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2832,56 +2927,59 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E45" s="3">
         <v>49600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>29500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>40900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>20200</v>
       </c>
       <c r="J45" s="3">
         <v>20200</v>
       </c>
       <c r="K45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="L45" s="3">
         <v>21300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>20400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>15000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2897,56 +2995,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>872800</v>
+      </c>
+      <c r="E46" s="3">
         <v>969100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>919300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>907000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>919700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>878400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>894000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>994700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1088800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1051500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1075800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1123400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1086400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1181100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>200400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,8 +3063,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3027,56 +3131,59 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E48" s="3">
         <v>48400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>51400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>49500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>49300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>47800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>49000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,56 +3199,59 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>567100</v>
+      </c>
+      <c r="E49" s="3">
         <v>593500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>614300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>609400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>602100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>612500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>608700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>473100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>463500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>463000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>447000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>321500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>317800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>315700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>261800</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,56 +3403,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E52" s="3">
         <v>97000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>107100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>41400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>38000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>52000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,56 +3539,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1588800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1708000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1692100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1611500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1604600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1567100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1592000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1538300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1607600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1614400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1586900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1511000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1470100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1546800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>502400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,56 +3661,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E57" s="3">
         <v>32900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8600</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,13 +3727,16 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7000</v>
+        <v>8800</v>
       </c>
       <c r="E58" s="3">
         <v>7000</v>
@@ -3644,8 +3777,8 @@
       <c r="Q58" s="3">
         <v>7000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>7000</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3662,56 +3795,59 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E59" s="3">
         <v>77900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>68700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>49600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>51600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>67100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>55800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>39500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>48400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>40100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>40900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>39100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>44400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,56 +3863,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E60" s="3">
         <v>117800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>69000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>76300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>85000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>79600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>59400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>81100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>72700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>65500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>63000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>60200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>60000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3792,56 +3931,59 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>647700</v>
+      </c>
+      <c r="E61" s="3">
         <v>648700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>649800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>650800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>651800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>652800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>653800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>654800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>655900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>656900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>657900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>658900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>659900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>688900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>689900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3857,56 +3999,59 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E62" s="3">
         <v>60100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>64400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>64300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>61700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>39000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>39200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>39300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>41300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>42200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3922,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,56 +4271,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>826800</v>
+      </c>
+      <c r="E66" s="3">
         <v>826700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>796700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>784000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>789800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>778700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>774100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>751800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>775900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>768000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>762500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>761900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>758800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>790400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>792200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4182,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4382,11 +4549,11 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>737000</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,56 +4637,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1457400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,56 +4909,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>762000</v>
+      </c>
+      <c r="E76" s="3">
         <v>881300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>895400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>827500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>814800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>788400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>817900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>786500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>831700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>846400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>824400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>749100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>711400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>756400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-38500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>58800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-41700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-39900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>31100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-298300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>27300</v>
       </c>
       <c r="R81" s="3">
         <v>27300</v>
       </c>
       <c r="S81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="T81" s="3">
         <v>15200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11600</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,59 +5214,60 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E83" s="3">
         <v>33000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5082,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,59 +5620,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E89" s="3">
         <v>60300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>29900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>32300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>33700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>51000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>49800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>48600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>34900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>45500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>32700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>38200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>45600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5472,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,59 +5716,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5562,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,59 +5918,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-163600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-34400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-132700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-73500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5757,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,59 +6284,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-125600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-91400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-111400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>992100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>27600</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6107,8 +6352,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,59 +6420,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-122600</v>
+      </c>
+      <c r="E102" s="3">
         <v>32900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-114900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-95700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>29100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-98700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>21800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-106300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>951300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>30800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>69800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6235,6 +6486,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>197900</v>
+      </c>
+      <c r="E8" s="3">
         <v>196600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>180000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>189700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>184000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>184100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>187300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>191800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>203300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>213300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>195100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>176600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>160400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>153500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>140500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>123300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>133400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>113300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>101700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>91500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>81700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E9" s="3">
         <v>15200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>16300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16700</v>
-      </c>
-      <c r="H9" s="3">
-        <v>17400</v>
       </c>
       <c r="I9" s="3">
         <v>17400</v>
       </c>
       <c r="J9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="K9" s="3">
         <v>18000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2900</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>185400</v>
+      </c>
+      <c r="E10" s="3">
         <v>181400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>161300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>173400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>167300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>166700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>169900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>173800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>191000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>199400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>183800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>165500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>150000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>144300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>133000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>116500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>127400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>108700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>98300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>88400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>78800</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E12" s="3">
         <v>32000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>39600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>36800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>35900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>35400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>35100</v>
       </c>
       <c r="M12" s="3">
         <v>35100</v>
       </c>
       <c r="N12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="O12" s="3">
         <v>29600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5600</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,40 +1141,43 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2400</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-8500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>18700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1165,11 +1185,11 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1177,12 +1197,12 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>4900</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1192,76 +1212,82 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E15" s="3">
         <v>43600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>33000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>15500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>10200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2600</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>190500</v>
+      </c>
+      <c r="E17" s="3">
         <v>214900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>220500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>171400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>174500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>182400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>203000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>195800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>183600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>201500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>188100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>177000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>165400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>453000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>202100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>81600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>89700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>82400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>63900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>53500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>53700</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-40500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-299500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-61600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>41700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>43700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>30900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>37800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>38000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>28000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,38 +1478,39 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E20" s="3">
         <v>8500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1487,128 +1521,134 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>100</v>
+      </c>
+      <c r="U20" s="3">
         <v>-2900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E21" s="3">
         <v>33800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>42200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>31700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>22700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-295000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-56500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>46300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>48100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>44000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E22" s="3">
         <v>14800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>5900</v>
       </c>
       <c r="L22" s="3">
         <v>5900</v>
@@ -1623,170 +1663,179 @@
         <v>5900</v>
       </c>
       <c r="P22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Q22" s="3">
         <v>6200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>10100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-46600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-305600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-67900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>35000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>35100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>17900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>25300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>25000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>14700</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-46700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-8700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>45800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-37300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-12600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-17900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-38500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>58800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-39900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>31100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-298300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="R26" s="3">
-        <v>27300</v>
       </c>
       <c r="S26" s="3">
         <v>27300</v>
       </c>
       <c r="T26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="U26" s="3">
         <v>15200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>19600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>11600</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-38500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>58800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>12300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-39900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>31100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-298300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="R27" s="3">
-        <v>27300</v>
       </c>
       <c r="S27" s="3">
         <v>27300</v>
       </c>
       <c r="T27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="U27" s="3">
         <v>15200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>19600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>11600</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,38 +2328,41 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2303,102 +2373,108 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U32" s="3">
         <v>2900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-38500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>58800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-39900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>31100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-298300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="R33" s="3">
-        <v>27300</v>
       </c>
       <c r="S33" s="3">
         <v>27300</v>
       </c>
       <c r="T33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="U33" s="3">
         <v>15200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>19600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11600</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-38500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>58800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-39900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>31100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-298300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="R35" s="3">
-        <v>27300</v>
       </c>
       <c r="S35" s="3">
         <v>27300</v>
       </c>
       <c r="T35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="U35" s="3">
         <v>15200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>19600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11600</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,59 +2744,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>533300</v>
+      </c>
+      <c r="E41" s="3">
         <v>672300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>794900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>762000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>761100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>757200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>728800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>730500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>845400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>941100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>912000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>894700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>990500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>968700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1075000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>126600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,59 +2884,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E43" s="3">
         <v>147100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>124600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>123400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>116400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>121700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>124300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>143200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>129100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>126400</v>
       </c>
       <c r="M43" s="3">
         <v>126400</v>
       </c>
       <c r="N43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="O43" s="3">
         <v>166800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>115800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>97300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>92300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>58800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,59 +3026,62 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E45" s="3">
         <v>53300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>49600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>40900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>20200</v>
       </c>
       <c r="K45" s="3">
         <v>20200</v>
       </c>
       <c r="L45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="M45" s="3">
         <v>21300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,59 +3097,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>732800</v>
+      </c>
+      <c r="E46" s="3">
         <v>872800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>969100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>919300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>907000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>919700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>878400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>894000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>994700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1088800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1051500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1075800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1123400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1086400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1181100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3066,8 +3168,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,59 +3239,62 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E48" s="3">
         <v>45900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>48400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>51500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>53700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>51400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>49500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>49300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>47800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>49000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>46100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35500</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,59 +3310,62 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>572900</v>
+      </c>
+      <c r="E49" s="3">
         <v>567100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>593500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>614300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>609400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>602100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>612500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>608700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>473100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>463500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>463000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>447000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>321500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>317800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>315700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>261800</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,59 +3523,62 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E52" s="3">
         <v>103000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>97000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>107100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>27200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>52000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,59 +3665,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1454000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1588800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1708000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1692100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1611500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1604600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1567100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1592000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1538300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1607600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1614400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1586900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1511000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1470100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1546800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>502400</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,59 +3792,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E57" s="3">
         <v>36300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8600</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,16 +3861,19 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8800</v>
-      </c>
-      <c r="E58" s="3">
-        <v>7000</v>
       </c>
       <c r="F58" s="3">
         <v>7000</v>
@@ -3780,8 +3914,8 @@
       <c r="R58" s="3">
         <v>7000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>7000</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3798,59 +3932,62 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E59" s="3">
         <v>77500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>77900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>68700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>49600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>51600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>67100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>55800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>56600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>48400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>40100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>40900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>39100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>44400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,59 +4003,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>116500</v>
+      </c>
+      <c r="E60" s="3">
         <v>122600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>117800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>82600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>69000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>76300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>85000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>79600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>59400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>81100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>72700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>65500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>63000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>59600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>60200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>60000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,59 +4074,62 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>646700</v>
+      </c>
+      <c r="E61" s="3">
         <v>647700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>648700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>649800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>650800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>651800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>652800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>653800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>654800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>655900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>656900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>657900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>658900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>659900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>688900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>689900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4002,59 +4145,62 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E62" s="3">
         <v>56600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>60100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>64400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>64300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>61700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>39000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>39200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>40000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>39300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>41300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>42200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,59 +4429,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>822900</v>
+      </c>
+      <c r="E66" s="3">
         <v>826800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>826700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>796700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>784000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>789800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>778700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>774100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>751800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>775900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>768000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>762500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>761900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>758800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>790400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>792200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4552,11 +4720,11 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>737000</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,59 +4811,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1458400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,59 +5095,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>631100</v>
+      </c>
+      <c r="E76" s="3">
         <v>762000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>881300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>895400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>827500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>814800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>788400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>817900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>786500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>831700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>846400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>824400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>749100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>711400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>756400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-38500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>58800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-39900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>31100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-298300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="R81" s="3">
-        <v>27300</v>
       </c>
       <c r="S81" s="3">
         <v>27300</v>
       </c>
       <c r="T81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="U81" s="3">
         <v>15200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>19600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11600</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,62 +5413,63 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E83" s="3">
         <v>43600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4300</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,62 +5837,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E89" s="3">
         <v>15900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>60300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>29900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>32300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>33700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>51000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>49800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>48600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>34900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>45500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>38200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>45600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,62 +5937,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,62 +6148,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-163600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-132700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-73500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3400</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,62 +6530,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-161000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-125600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-13700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-91400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-111400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>992100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27600</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6355,8 +6601,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,62 +6672,65 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-122600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>28400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-114900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-95700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>29100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-98700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>21800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-106300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>951300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>30800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>69800</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6489,6 +6741,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E8" s="3">
         <v>197900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>196600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>180000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>189700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>184000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>184100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>187300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>191800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>203300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>213300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>195100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>176600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>160400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>153500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>140500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>123300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>133400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>113300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>101700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>91500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>81700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E9" s="3">
         <v>12500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>17400</v>
       </c>
       <c r="J9" s="3">
         <v>17400</v>
       </c>
       <c r="K9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="L9" s="3">
         <v>18000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>188700</v>
+      </c>
+      <c r="E10" s="3">
         <v>185400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>181400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>161300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>173400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>167300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>166700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>169900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>173800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>191000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>199400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>183800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>165500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>150000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>144300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>133000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>116500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>127400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>108700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>98300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>88400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>78800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E12" s="3">
         <v>31000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>32000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>39600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>36800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>35900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>35100</v>
       </c>
       <c r="N12" s="3">
         <v>35100</v>
       </c>
       <c r="O12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="P12" s="3">
         <v>29600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>26200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5600</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1153,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2400</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-8500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>18700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1188,11 +1208,11 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1200,12 +1220,12 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>4900</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1215,79 +1235,85 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E15" s="3">
         <v>15900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>43600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>33000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>15500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>10600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>10200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2600</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E17" s="3">
         <v>190500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>214900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>220500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>171400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>174500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>182400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>203000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>195800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>183600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>201500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>188100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>177000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>165400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>453000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>202100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>81600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>89700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>82400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>53500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53700</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E18" s="3">
         <v>7400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-40500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-299500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-61600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>41700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>43700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>30900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>37800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>38000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>28000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,41 +1512,42 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E20" s="3">
         <v>7500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1524,105 +1558,111 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>-2900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E21" s="3">
         <v>30900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>33800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>42200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>31700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>22700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>31200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>17200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-295000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-56500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>46300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>48100</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>44000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1630,28 +1670,28 @@
         <v>14600</v>
       </c>
       <c r="E22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F22" s="3">
         <v>14800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>5900</v>
       </c>
       <c r="M22" s="3">
         <v>5900</v>
@@ -1666,176 +1706,185 @@
         <v>5900</v>
       </c>
       <c r="Q22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="R22" s="3">
         <v>6200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13400</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E23" s="3">
         <v>300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-46600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-305600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-67900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>35000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>35100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>25300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>25000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>14700</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-8100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-46700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-8700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>45800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-37300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-17900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3200</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>58800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-41700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-39900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>31100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-298300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="S26" s="3">
-        <v>27300</v>
       </c>
       <c r="T26" s="3">
         <v>27300</v>
       </c>
       <c r="U26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="V26" s="3">
         <v>15200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>11600</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>58800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-39900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>31100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-298300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="S27" s="3">
-        <v>27300</v>
       </c>
       <c r="T27" s="3">
         <v>27300</v>
       </c>
       <c r="U27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="V27" s="3">
         <v>15200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>11600</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,41 +2398,44 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2376,105 +2446,111 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>2900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>58800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-41700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-39900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>31100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-298300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="S33" s="3">
-        <v>27300</v>
       </c>
       <c r="T33" s="3">
         <v>27300</v>
       </c>
       <c r="U33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="V33" s="3">
         <v>15200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>19600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>11600</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>58800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-41700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-39900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>31100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-298300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="S35" s="3">
-        <v>27300</v>
       </c>
       <c r="T35" s="3">
         <v>27300</v>
       </c>
       <c r="U35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="V35" s="3">
         <v>15200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>19600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>11600</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,62 +2831,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>524900</v>
+      </c>
+      <c r="E41" s="3">
         <v>533300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>672300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>794900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>762000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>761100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>757200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>728800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>730500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>845400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>941100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>912000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>894700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>990500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>968700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1075000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,8 +2903,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,62 +2977,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>174700</v>
+      </c>
+      <c r="E43" s="3">
         <v>147000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>147100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>124600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>123400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>116400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>121700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>124300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>143200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>129100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>126400</v>
       </c>
       <c r="N43" s="3">
         <v>126400</v>
       </c>
       <c r="O43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="P43" s="3">
         <v>166800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>115800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>97300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>92300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>58800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,8 +3051,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,62 +3125,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E45" s="3">
         <v>52500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>53300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>49600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>40900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>20200</v>
       </c>
       <c r="L45" s="3">
         <v>20200</v>
       </c>
       <c r="M45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="N45" s="3">
         <v>21300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,62 +3199,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>750600</v>
+      </c>
+      <c r="E46" s="3">
         <v>732800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>872800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>969100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>919300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>907000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>919700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>878400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>894000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>994700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1088800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1051500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1075800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1123400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1086400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1181100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>200400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,8 +3273,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,62 +3347,65 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E48" s="3">
         <v>46300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>48400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>51500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>53700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>55700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>50300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>49500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>49300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>47800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>46100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35500</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3313,62 +3421,65 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>578600</v>
+      </c>
+      <c r="E49" s="3">
         <v>572900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>567100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>593500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>614300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>609400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>602100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>612500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>608700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>473100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>463500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>463000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>447000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>321500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>317800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>315700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>261800</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,62 +3643,65 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E52" s="3">
         <v>102000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>103000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>97000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>107100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>41400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>20900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>52000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,62 +3791,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1475400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1454000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1588800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1708000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1692100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1611500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1604600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1567100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1592000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1538300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1607600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1614400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1586900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1511000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1470100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1546800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>502400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,62 +3923,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E57" s="3">
         <v>33500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8600</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3995,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3873,10 +4007,10 @@
         <v>7000</v>
       </c>
       <c r="E58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F58" s="3">
         <v>8800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>7000</v>
       </c>
       <c r="G58" s="3">
         <v>7000</v>
@@ -3917,8 +4051,8 @@
       <c r="S58" s="3">
         <v>7000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>7000</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -3935,62 +4069,65 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E59" s="3">
         <v>76000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>77500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>77900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>68700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>49600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>51600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>67100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>56600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>40100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>39100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>44400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,62 +4143,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E60" s="3">
         <v>116500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>122600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>117800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>82600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>69000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>76300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>85000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>79600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>59400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>81100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>72700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>65500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>63000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>59600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>60200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>60000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4077,62 +4217,65 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>645600</v>
+      </c>
+      <c r="E61" s="3">
         <v>646700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>647700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>648700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>649800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>650800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>651800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>652800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>653800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>654800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>655900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>656900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>657900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>658900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>659900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>688900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>689900</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,62 +4291,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E62" s="3">
         <v>59700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>56600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>60100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>64400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>64300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>61700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>37600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>39000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>39200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>40000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>39300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>41300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>42200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,62 +4587,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>806000</v>
+      </c>
+      <c r="E66" s="3">
         <v>822900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>826800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>826700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>796700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>784000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>789800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>778700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>774100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>751800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>775900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>768000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>762500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>761900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>758800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>790400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>792200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4723,11 +4891,11 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>737000</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,62 +4985,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1451700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1458400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,62 +5281,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>669400</v>
+      </c>
+      <c r="E76" s="3">
         <v>631100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>762000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>881300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>895400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>827500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>814800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>788400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>817900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>786500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>831700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>846400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>824400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>749100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>711400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>756400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>58800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-41700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-39900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>31100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-298300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="S81" s="3">
-        <v>27300</v>
       </c>
       <c r="T81" s="3">
         <v>27300</v>
       </c>
       <c r="U81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="V81" s="3">
         <v>15200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>19600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>11600</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,65 +5612,66 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E83" s="3">
         <v>15900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>43600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,65 +6054,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E89" s="3">
         <v>42600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>60300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>32300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>31900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>51000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>30100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>49800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>48600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>34900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>45500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>38200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>45600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5911,8 +6128,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,65 +6158,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-15300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,65 +6378,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-163600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-34400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-132700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-73500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,65 +6776,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-161000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-125600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-21700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-91400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-111400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>992100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>27600</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6604,8 +6850,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,65 +6924,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-139000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-122600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>28400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-114900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-95700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>29100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-98700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>21800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-106300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>951300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>30800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>69800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6744,6 +6996,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -656,340 +656,353 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>195300</v>
+      </c>
+      <c r="E8" s="3">
         <v>200600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>197900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>196600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>180000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>189700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>184000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>184100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>187300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>191800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>203300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>213300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>195100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>176600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>160400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>153500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>140500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>123300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>133400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>113300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>101700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>91500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>81700</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E9" s="3">
         <v>11900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12500</v>
       </c>
-      <c r="F9" s="3">
-        <v>15200</v>
-      </c>
       <c r="G9" s="3">
+        <v>10700</v>
+      </c>
+      <c r="H9" s="3">
         <v>18700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16700</v>
-      </c>
-      <c r="J9" s="3">
-        <v>17400</v>
       </c>
       <c r="K9" s="3">
         <v>17400</v>
       </c>
       <c r="L9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="M9" s="3">
         <v>18000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2900</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>183600</v>
+      </c>
+      <c r="E10" s="3">
         <v>188700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>185400</v>
       </c>
-      <c r="F10" s="3">
-        <v>181400</v>
-      </c>
       <c r="G10" s="3">
-        <v>161300</v>
+        <v>186000</v>
       </c>
       <c r="H10" s="3">
-        <v>173400</v>
+        <v>161200</v>
       </c>
       <c r="I10" s="3">
+        <v>173300</v>
+      </c>
+      <c r="J10" s="3">
         <v>167300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>166700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>169900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>173800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>191000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>199400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>183800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>165500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>150000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>144300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>133000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>116500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>127400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>108700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>98300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>88400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>78800</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,82 +1029,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E12" s="3">
         <v>30900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31000</v>
       </c>
-      <c r="F12" s="3">
-        <v>32000</v>
-      </c>
       <c r="G12" s="3">
+        <v>22600</v>
+      </c>
+      <c r="H12" s="3">
         <v>39600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>36800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>35000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>35100</v>
       </c>
       <c r="O12" s="3">
         <v>35100</v>
       </c>
       <c r="P12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>29600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>26200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>23700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>15800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5600</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,46 +1181,49 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
-        <v>200</v>
+        <v>13000</v>
       </c>
       <c r="G14" s="3">
-        <v>2400</v>
+        <v>76900</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>1800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-8500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>18700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1211,11 +1231,11 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1223,12 +1243,12 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
         <v>4900</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1238,82 +1258,88 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E15" s="3">
         <v>17000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15900</v>
       </c>
-      <c r="F15" s="3">
-        <v>43600</v>
-      </c>
       <c r="G15" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="H15" s="3">
         <v>33000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>10600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>10200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>8400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2600</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1363,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>174800</v>
+      </c>
+      <c r="E17" s="3">
         <v>180700</v>
       </c>
-      <c r="E17" s="3">
-        <v>190500</v>
-      </c>
       <c r="F17" s="3">
-        <v>214900</v>
+        <v>177500</v>
       </c>
       <c r="G17" s="3">
-        <v>220500</v>
+        <v>138000</v>
       </c>
       <c r="H17" s="3">
+        <v>218300</v>
+      </c>
+      <c r="I17" s="3">
         <v>171400</v>
       </c>
-      <c r="I17" s="3">
-        <v>174500</v>
-      </c>
       <c r="J17" s="3">
+        <v>172700</v>
+      </c>
+      <c r="K17" s="3">
         <v>182400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>203000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>195800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>183600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>201500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>188100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>177000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>165400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>453000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>202100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>81600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>89700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>82400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>63900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>53700</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E18" s="3">
         <v>19900</v>
       </c>
-      <c r="E18" s="3">
-        <v>7400</v>
-      </c>
       <c r="F18" s="3">
-        <v>-18300</v>
+        <v>20400</v>
       </c>
       <c r="G18" s="3">
-        <v>-40500</v>
+        <v>58600</v>
       </c>
       <c r="H18" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="I18" s="3">
         <v>18300</v>
       </c>
-      <c r="I18" s="3">
-        <v>9500</v>
-      </c>
       <c r="J18" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K18" s="3">
         <v>1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-299500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-61600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>41700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>30900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>37800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>38000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28000</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,44 +1546,45 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>7500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>8500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>8600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>7800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>7200</v>
-      </c>
-      <c r="J20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>5500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1561,140 +1595,146 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-2900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>43200</v>
+        <v>35300</v>
       </c>
       <c r="E21" s="3">
-        <v>30900</v>
+        <v>36800</v>
       </c>
       <c r="F21" s="3">
-        <v>33800</v>
+        <v>36300</v>
       </c>
       <c r="G21" s="3">
-        <v>1100</v>
+        <v>55600</v>
       </c>
       <c r="H21" s="3">
-        <v>42200</v>
+        <v>-5300</v>
       </c>
       <c r="I21" s="3">
-        <v>31700</v>
+        <v>34400</v>
       </c>
       <c r="J21" s="3">
+        <v>26200</v>
+      </c>
+      <c r="K21" s="3">
         <v>22700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>22400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-295000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-56500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>46300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>48100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>44000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>14600</v>
+        <v>12400</v>
       </c>
       <c r="E22" s="3">
         <v>14600</v>
       </c>
       <c r="F22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="G22" s="3">
         <v>14800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>5900</v>
       </c>
       <c r="N22" s="3">
         <v>5900</v>
@@ -1709,182 +1749,191 @@
         <v>5900</v>
       </c>
       <c r="R22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="S22" s="3">
         <v>6200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13400</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E23" s="3">
         <v>11600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-46600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-305600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-67900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>35000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>35100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>17900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>25300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>25000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>14700</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-8100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-46700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-8700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>45800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-12600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-17900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3200</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E26" s="3">
         <v>6700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-38500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>58800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-41700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-39900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-298300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="T26" s="3">
-        <v>27300</v>
       </c>
       <c r="U26" s="3">
         <v>27300</v>
       </c>
       <c r="V26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="W26" s="3">
         <v>15200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11600</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E27" s="3">
         <v>6700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-38500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>58800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-39900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-298300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="T27" s="3">
-        <v>27300</v>
       </c>
       <c r="U27" s="3">
         <v>27300</v>
       </c>
       <c r="V27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="W27" s="3">
         <v>15200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11600</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,44 +2468,47 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-7200</v>
-      </c>
-      <c r="J32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-5500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2449,108 +2519,114 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>2900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E33" s="3">
         <v>6700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-38500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>58800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-39900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-298300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="T33" s="3">
-        <v>27300</v>
       </c>
       <c r="U33" s="3">
         <v>27300</v>
       </c>
       <c r="V33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="W33" s="3">
         <v>15200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11600</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E35" s="3">
         <v>6700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-38500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>58800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-39900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-298300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="T35" s="3">
-        <v>27300</v>
       </c>
       <c r="U35" s="3">
         <v>27300</v>
       </c>
       <c r="V35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="W35" s="3">
         <v>15200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11600</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,65 +2918,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>423800</v>
+      </c>
+      <c r="E41" s="3">
         <v>524900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>533300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>672300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>794900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>762000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>761100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>757200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>728800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>730500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>845400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>941100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>912000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>894700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>990500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>968700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1075000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>126600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,8 +2993,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,65 +3070,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>180400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>203800</v>
+      </c>
+      <c r="F43" s="3">
         <v>174700</v>
       </c>
-      <c r="E43" s="3">
-        <v>147000</v>
-      </c>
-      <c r="F43" s="3">
-        <v>147100</v>
-      </c>
       <c r="G43" s="3">
-        <v>124600</v>
+        <v>175500</v>
       </c>
       <c r="H43" s="3">
+        <v>145200</v>
+      </c>
+      <c r="I43" s="3">
         <v>123400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>116400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>121700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>124300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>143200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>129100</v>
-      </c>
-      <c r="N43" s="3">
-        <v>126400</v>
       </c>
       <c r="O43" s="3">
         <v>126400</v>
       </c>
       <c r="P43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="Q43" s="3">
         <v>166800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>115800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>97300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>92300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>58800</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,31 +3147,34 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3128,65 +3224,68 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>51000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>52500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>53300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>49600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>33900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>29500</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>40900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25400</v>
-      </c>
-      <c r="L45" s="3">
-        <v>20200</v>
       </c>
       <c r="M45" s="3">
         <v>20200</v>
       </c>
       <c r="N45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="O45" s="3">
         <v>21300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>20400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,65 +3301,68 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>626800</v>
+      </c>
+      <c r="E46" s="3">
         <v>750600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>732800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>872800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>969100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>919300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>907000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>919700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>878400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>894000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>994700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1088800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1051500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1075800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1123400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1086400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1181100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>200400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,31 +3378,34 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3350,65 +3455,68 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E48" s="3">
         <v>44400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>46300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>48400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>51500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>53700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>55700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>49500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>49300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>47800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>46100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35500</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3424,65 +3532,68 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>584700</v>
+      </c>
+      <c r="E49" s="3">
         <v>578600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>572900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>567100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>593500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>614300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>609400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>602100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>612500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>608700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>473100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>463500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>463000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>447000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>321500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>317800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>315700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>261800</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,65 +3763,68 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>101900</v>
+        <v>19900</v>
       </c>
       <c r="E52" s="3">
-        <v>102000</v>
+        <v>21600</v>
       </c>
       <c r="F52" s="3">
-        <v>103000</v>
+        <v>21800</v>
       </c>
       <c r="G52" s="3">
-        <v>97000</v>
+        <v>22800</v>
       </c>
       <c r="H52" s="3">
-        <v>107100</v>
+        <v>24300</v>
       </c>
       <c r="I52" s="3">
-        <v>41400</v>
+        <v>27300</v>
       </c>
       <c r="J52" s="3">
+        <v>24200</v>
+      </c>
+      <c r="K52" s="3">
         <v>27200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>26000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>52000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4700</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,65 +3917,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1354800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1475400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1454000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1588800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1708000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1692100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1611500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1604600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1567100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1592000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1538300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1607600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1614400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1586900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1511000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1470100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1546800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>502400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,8 +3994,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,65 +4054,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E57" s="3">
         <v>16900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8600</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,31 +4129,34 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7000</v>
+        <v>9300</v>
       </c>
       <c r="E58" s="3">
-        <v>7000</v>
+        <v>12400</v>
       </c>
       <c r="F58" s="3">
-        <v>8800</v>
+        <v>12200</v>
       </c>
       <c r="G58" s="3">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H58" s="3">
-        <v>7000</v>
+        <v>10400</v>
       </c>
       <c r="I58" s="3">
-        <v>7000</v>
+        <v>9800</v>
       </c>
       <c r="J58" s="3">
-        <v>7000</v>
+        <v>8900</v>
       </c>
       <c r="K58" s="3">
         <v>7000</v>
@@ -4054,8 +4188,8 @@
       <c r="T58" s="3">
         <v>7000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>7000</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4072,65 +4206,68 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>78600</v>
+        <v>16700</v>
       </c>
       <c r="E59" s="3">
-        <v>76000</v>
+        <v>6000</v>
       </c>
       <c r="F59" s="3">
-        <v>77500</v>
+        <v>6500</v>
       </c>
       <c r="G59" s="3">
-        <v>77900</v>
+        <v>7100</v>
       </c>
       <c r="H59" s="3">
-        <v>68700</v>
+        <v>15100</v>
       </c>
       <c r="I59" s="3">
-        <v>49600</v>
+        <v>26300</v>
       </c>
       <c r="J59" s="3">
+        <v>14500</v>
+      </c>
+      <c r="K59" s="3">
         <v>51600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>67100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>55800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>56600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>40900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>42200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>44400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4146,65 +4283,68 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E60" s="3">
         <v>102500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>116500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>122600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>117800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>82600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>69000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>76300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>85000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>79600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>59400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>81100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>72700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>65500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>63000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>59600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>60200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>60000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4220,65 +4360,68 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>645600</v>
+        <v>535300</v>
       </c>
       <c r="E61" s="3">
-        <v>646700</v>
+        <v>695000</v>
       </c>
       <c r="F61" s="3">
-        <v>647700</v>
+        <v>698000</v>
       </c>
       <c r="G61" s="3">
-        <v>648700</v>
+        <v>696100</v>
       </c>
       <c r="H61" s="3">
-        <v>649800</v>
+        <v>701100</v>
       </c>
       <c r="I61" s="3">
-        <v>650800</v>
+        <v>704600</v>
       </c>
       <c r="J61" s="3">
+        <v>707100</v>
+      </c>
+      <c r="K61" s="3">
         <v>651800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>652800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>653800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>654800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>655900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>656900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>657900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>658900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>659900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>688900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>689900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4294,65 +4437,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>57900</v>
+        <v>8800</v>
       </c>
       <c r="E62" s="3">
-        <v>59700</v>
+        <v>8600</v>
       </c>
       <c r="F62" s="3">
-        <v>56600</v>
+        <v>8400</v>
       </c>
       <c r="G62" s="3">
-        <v>60100</v>
+        <v>8200</v>
       </c>
       <c r="H62" s="3">
-        <v>64400</v>
+        <v>7800</v>
       </c>
       <c r="I62" s="3">
-        <v>64300</v>
+        <v>9600</v>
       </c>
       <c r="J62" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K62" s="3">
         <v>61700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>39000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>38400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>39200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>40000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>39300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>41300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>42200</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,65 +4745,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>658400</v>
+      </c>
+      <c r="E66" s="3">
         <v>806000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>822900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>826800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>826700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>796700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>784000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>789800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>778700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>774100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>751800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>775900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>768000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>762500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>761900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>758800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>790400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>792200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4822,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4894,11 +5062,11 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>737000</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,65 +5159,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1447800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1451700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1458400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5062,8 +5236,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,65 +5467,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>696400</v>
+      </c>
+      <c r="E76" s="3">
         <v>669400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>631100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>762000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>881300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>895400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>827500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>814800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>788400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>817900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>786500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>831700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>846400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>824400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>749100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>711400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>756400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5544,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E81" s="3">
         <v>6700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-38500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>58800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-39900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-298300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="T81" s="3">
-        <v>27300</v>
       </c>
       <c r="U81" s="3">
         <v>27300</v>
       </c>
       <c r="V81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="W81" s="3">
         <v>15200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11600</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,68 +5811,69 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>17000</v>
+        <v>33000</v>
       </c>
       <c r="E83" s="3">
-        <v>15900</v>
+        <v>16100</v>
       </c>
       <c r="F83" s="3">
-        <v>43600</v>
+        <v>14900</v>
       </c>
       <c r="G83" s="3">
-        <v>33000</v>
+        <v>-10900</v>
       </c>
       <c r="H83" s="3">
-        <v>16100</v>
+        <v>14000</v>
       </c>
       <c r="I83" s="3">
-        <v>14900</v>
+        <v>13300</v>
       </c>
       <c r="J83" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K83" s="3">
         <v>15500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,68 +6271,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E89" s="3">
         <v>9700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>42600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>60300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>31900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>51000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>30100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>49800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>48600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>34900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>45500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>32700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>38200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>45600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6131,8 +6348,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,68 +6379,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-17200</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
-        <v>-20600</v>
+        <v>-300</v>
       </c>
       <c r="F91" s="3">
-        <v>-12900</v>
+        <v>-400</v>
       </c>
       <c r="G91" s="3">
-        <v>-13600</v>
+        <v>-400</v>
       </c>
       <c r="H91" s="3">
-        <v>-15000</v>
+        <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>-14300</v>
+        <v>-300</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-15300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,68 +6608,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-20600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-163600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-132700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-73500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3400</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6455,8 +6685,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,31 +6716,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,68 +7022,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-172100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-161000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-125600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-21700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-91400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-14000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-111400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>992100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>27600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6853,31 +7099,34 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6927,68 +7176,71 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-101100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-139000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-122600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>28400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-114900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-95700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>29100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-98700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>21800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-106300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>951300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>30800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>69800</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6999,6 +7251,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -656,353 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>198600</v>
+      </c>
+      <c r="E8" s="3">
         <v>195300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>197900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>196600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>180000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>189700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>184000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>184100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>187300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>191800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>203300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>213300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>195100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>176600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>160400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>153500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>140500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>123300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>133400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>113300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>101700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>91500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>81700</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E9" s="3">
         <v>11700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16700</v>
-      </c>
-      <c r="K9" s="3">
-        <v>17400</v>
       </c>
       <c r="L9" s="3">
         <v>17400</v>
       </c>
       <c r="M9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="N9" s="3">
         <v>18000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2900</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>186400</v>
+      </c>
+      <c r="E10" s="3">
         <v>183600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>188700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>185400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>186000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>161200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>173300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>167300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>166700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>169900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>173800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>191000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>199400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>183800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>165500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>150000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>144300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>133000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>116500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>127400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>108700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>98300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>88400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>78800</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E12" s="3">
         <v>30100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>39600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>31300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>36800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>35900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>35400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>35000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>35100</v>
       </c>
       <c r="P12" s="3">
         <v>35100</v>
       </c>
       <c r="Q12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="R12" s="3">
         <v>29600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>26200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>23700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>15800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5600</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,49 +1200,52 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E14" s="3">
         <v>2100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>13000</v>
       </c>
-      <c r="G14" s="3">
-        <v>76900</v>
-      </c>
       <c r="H14" s="3">
+        <v>77000</v>
+      </c>
+      <c r="I14" s="3">
         <v>2200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-8500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>18700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1234,11 +1253,11 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1246,12 +1265,12 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>4900</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,85 +1280,91 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E15" s="3">
         <v>17500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>15900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>-3100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>33000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>13300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>10600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>10200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>8400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2600</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E17" s="3">
         <v>174800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>180700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>177500</v>
       </c>
-      <c r="G17" s="3">
-        <v>138000</v>
-      </c>
       <c r="H17" s="3">
+        <v>137900</v>
+      </c>
+      <c r="I17" s="3">
         <v>218300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>171400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>172700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>182400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>203000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>195800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>183600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>201500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>188100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>177000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>165400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>453000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>202100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>81600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>89700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>82400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>63900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>53500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>53700</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E18" s="3">
         <v>20400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20400</v>
       </c>
-      <c r="G18" s="3">
-        <v>58600</v>
-      </c>
       <c r="H18" s="3">
+        <v>58700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-38300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-299500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-61600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>41700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>30900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>37800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>38000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>28000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,17 +1579,18 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>2700</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1573,21 +1606,21 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>5500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1598,146 +1631,152 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3">
         <v>-2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E21" s="3">
         <v>35300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>36800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>36300</v>
       </c>
-      <c r="G21" s="3">
-        <v>55600</v>
-      </c>
       <c r="H21" s="3">
+        <v>55700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-5300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>34400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>22700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>31200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>22400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-295000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-56500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>46300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>48100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>44000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E22" s="3">
         <v>12400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>14600</v>
       </c>
       <c r="F22" s="3">
         <v>14600</v>
       </c>
       <c r="G22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="H22" s="3">
         <v>14800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>5900</v>
       </c>
       <c r="O22" s="3">
         <v>5900</v>
@@ -1752,188 +1791,197 @@
         <v>5900</v>
       </c>
       <c r="S22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="T22" s="3">
         <v>6200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13400</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E23" s="3">
         <v>8100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-46600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-305600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-67900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>35000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>35100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>17900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>25300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>25000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>14700</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E24" s="3">
         <v>4100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-8100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-46700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-8700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>45800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>19200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-37300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-12600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-7400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-17900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3200</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E26" s="3">
         <v>4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-38500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>58800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-41700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-39900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-298300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="U26" s="3">
-        <v>27300</v>
       </c>
       <c r="V26" s="3">
         <v>27300</v>
       </c>
       <c r="W26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="X26" s="3">
         <v>15200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11600</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E27" s="3">
         <v>4000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-38500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>58800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-41700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-39900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-298300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="U27" s="3">
-        <v>27300</v>
       </c>
       <c r="V27" s="3">
         <v>27300</v>
       </c>
       <c r="W27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="X27" s="3">
         <v>15200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>11600</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,17 +2537,20 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2700</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2497,21 +2566,21 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-5500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2522,111 +2591,117 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3">
         <v>2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E33" s="3">
         <v>4000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-38500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>58800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-41700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-39900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-298300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="U33" s="3">
-        <v>27300</v>
       </c>
       <c r="V33" s="3">
         <v>27300</v>
       </c>
       <c r="W33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="X33" s="3">
         <v>15200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11600</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E35" s="3">
         <v>4000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-38500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>58800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-41700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-39900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-298300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="U35" s="3">
-        <v>27300</v>
       </c>
       <c r="V35" s="3">
         <v>27300</v>
       </c>
       <c r="W35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="X35" s="3">
         <v>15200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11600</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,68 +3004,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>448300</v>
+      </c>
+      <c r="E41" s="3">
         <v>423800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>524900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>533300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>672300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>794900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>762000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>761100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>757200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>728800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>730500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>845400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>941100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>912000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>894700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>990500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>968700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1075000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>126600</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2996,8 +3082,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,68 +3162,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E43" s="3">
         <v>180400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>203800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>174700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>175500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>145200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>123400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>116400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>121700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>124300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>143200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>129100</v>
-      </c>
-      <c r="O43" s="3">
-        <v>126400</v>
       </c>
       <c r="P43" s="3">
         <v>126400</v>
       </c>
       <c r="Q43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="R43" s="3">
         <v>166800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>115800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>97300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>92300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>58800</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3150,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3176,8 +3271,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3227,8 +3322,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3253,42 +3351,42 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>40900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25400</v>
-      </c>
-      <c r="M45" s="3">
-        <v>20200</v>
       </c>
       <c r="N45" s="3">
         <v>20200</v>
       </c>
       <c r="O45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="P45" s="3">
         <v>21300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>14200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15000</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,68 +3402,71 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>659300</v>
+      </c>
+      <c r="E46" s="3">
         <v>626800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>750600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>732800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>872800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>969100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>919300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>907000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>919700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>878400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>894000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>994700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1088800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1051500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1075800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1123400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1086400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1181100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>200400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,8 +3482,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3402,13 +3506,13 @@
         <v>15000</v>
       </c>
       <c r="I47" s="3">
-        <v>17200</v>
+        <v>15000</v>
       </c>
       <c r="J47" s="3">
         <v>17200</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3458,68 +3562,71 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E48" s="3">
         <v>42500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>44400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>48400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>51500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>53700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>49500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>47800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>50800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>46100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35500</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3535,68 +3642,71 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>587700</v>
+      </c>
+      <c r="E49" s="3">
         <v>584700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>578600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>572900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>567100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>593500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>614300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>609400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>602100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>612500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>608700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>473100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>463500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>463000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>447000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>321500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>317800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>315700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>261800</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,68 +3882,71 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E52" s="3">
         <v>19900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>20900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>52000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,68 +4042,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1388100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1354800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1475400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1454000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1588800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1708000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1692100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1611500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1604600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1567100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1592000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1538300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1607600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1614400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1586900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1511000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1470100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1546800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>502400</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,68 +4184,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E57" s="3">
         <v>12400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8600</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4132,34 +4262,37 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E58" s="3">
         <v>9300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>7000</v>
       </c>
       <c r="L58" s="3">
         <v>7000</v>
@@ -4191,8 +4324,8 @@
       <c r="U58" s="3">
         <v>7000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>7000</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4209,68 +4342,71 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E59" s="3">
         <v>16700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>51600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>67100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>55800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>39500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>56600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>40100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>40900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>42200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>39100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>44400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4286,68 +4422,71 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E60" s="3">
         <v>114400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>102500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>116500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>122600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>117800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>82600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>69000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>76300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>85000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>79600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>59400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>81100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>72700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>65500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>63000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>59600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>60200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>60000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,68 +4502,71 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>532800</v>
+      </c>
+      <c r="E61" s="3">
         <v>535300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>695000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>698000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>696100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>701100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>704600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>707100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>651800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>652800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>653800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>654800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>655900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>656900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>657900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>658900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>659900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>688900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>689900</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4440,68 +4582,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E62" s="3">
         <v>8800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>61700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>40600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>39000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>38400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>39200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>40000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>39300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>41300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>42200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,68 +4902,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>663400</v>
+      </c>
+      <c r="E66" s="3">
         <v>658400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>806000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>822900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>826800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>826700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>796700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>784000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>789800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>778700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>774100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>751800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>775900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>768000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>762500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>761900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>758800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>790400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>792200</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5065,11 +5232,11 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>737000</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,68 +5332,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1441000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1447800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1451700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1458400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5239,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,68 +5652,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>724700</v>
+      </c>
+      <c r="E76" s="3">
         <v>696400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>669400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>631100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>762000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>881300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>895400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>827500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>814800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>788400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>817900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>786500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>831700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>846400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>824400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>749100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>711400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>756400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5547,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E81" s="3">
         <v>4000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-38500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>58800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-41700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-39900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-298300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="U81" s="3">
-        <v>27300</v>
       </c>
       <c r="V81" s="3">
         <v>27300</v>
       </c>
       <c r="W81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="X81" s="3">
         <v>15200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11600</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,71 +6009,72 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E83" s="3">
         <v>33000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-10900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4300</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5889,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,71 +6487,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E89" s="3">
         <v>86900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>42600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>60300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>29900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>32300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>51000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>30100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>48600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>34900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>45500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>32700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>38200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>45600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6351,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,71 +6599,72 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-400</v>
       </c>
       <c r="G91" s="3">
         <v>-400</v>
       </c>
       <c r="H91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6457,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,71 +6837,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-15900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-20600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-163600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-34400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-132700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-73500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3400</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6688,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,8 +6976,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,71 +7267,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-172100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-161000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-125600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-91400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-14000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-111400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>992100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>27600</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7102,8 +7347,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,8 +7376,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7179,71 +7427,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-101100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-139000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-122600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-114900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-95700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>29100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-98700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>21800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-106300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>951300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>30800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>69800</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7254,6 +7505,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E8" s="3">
         <v>198600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>195300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>197900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>196600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>180000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>189700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>184000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>184100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>187300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>191800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>203300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>213300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>195100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>176600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>160400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>153500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>140500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>123300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>133400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>113300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>101700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>91500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>81700</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E9" s="3">
         <v>12200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16700</v>
-      </c>
-      <c r="L9" s="3">
-        <v>17400</v>
       </c>
       <c r="M9" s="3">
         <v>17400</v>
       </c>
       <c r="N9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="O9" s="3">
         <v>18000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>11300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2900</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>189600</v>
+      </c>
+      <c r="E10" s="3">
         <v>186400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>183600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>188700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>185400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>186000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>161200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>173300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>167300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>166700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>169900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>173800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>191000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>199400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>183800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>165500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>150000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>144300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>133000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>116500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>127400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>108700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>98300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>88400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>78800</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E12" s="3">
         <v>31700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>30100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>39600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>36800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>35900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>35400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>35000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>35100</v>
       </c>
       <c r="Q12" s="3">
         <v>35100</v>
       </c>
       <c r="R12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="S12" s="3">
         <v>29600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>26200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>23700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>15800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>5600</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,52 +1220,55 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E14" s="3">
         <v>20400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>13000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>77000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>1800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-8500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>18700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1256,11 +1276,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1268,12 +1288,12 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
         <v>4900</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1283,88 +1303,94 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E15" s="3">
         <v>19100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>17000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>15900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>-3100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>33000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>15500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>10600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>8400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2600</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>175200</v>
+      </c>
+      <c r="E17" s="3">
         <v>160000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>174800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>180700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>177500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>137900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>218300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>171400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>172700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>182400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>203000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>195800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>183600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>201500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>188100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>177000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>165400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>453000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>202100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>81600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>89700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>82400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>63900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>53500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>53700</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E18" s="3">
         <v>38500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>20400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>58700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-38300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-299500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-61600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>41700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>43700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>30900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>37800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>38000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>28000</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,20 +1613,21 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>2700</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1609,21 +1643,21 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1634,152 +1668,158 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E21" s="3">
         <v>57600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>35300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>36800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>36300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>55700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>34400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>31200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-295000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-56500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>46300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>48100</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>44000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E22" s="3">
         <v>11400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>14600</v>
       </c>
       <c r="G22" s="3">
         <v>14600</v>
       </c>
       <c r="H22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="I22" s="3">
         <v>14800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>5900</v>
       </c>
       <c r="P22" s="3">
         <v>5900</v>
@@ -1794,194 +1834,203 @@
         <v>5900</v>
       </c>
       <c r="T22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="U22" s="3">
         <v>6200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13400</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E23" s="3">
         <v>11400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-24600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-46600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-305600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-67900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>35000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>35100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>25300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>25000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>14700</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E24" s="3">
         <v>4700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-8100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-46700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-8700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>45800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-37300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-12600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-7400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-17900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3200</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E26" s="3">
         <v>6700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>58800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-41700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-39900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-298300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="V26" s="3">
-        <v>27300</v>
       </c>
       <c r="W26" s="3">
         <v>27300</v>
       </c>
       <c r="X26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Y26" s="3">
         <v>15200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>11600</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E27" s="3">
         <v>6700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>58800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-41700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-39900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-298300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="V27" s="3">
-        <v>27300</v>
       </c>
       <c r="W27" s="3">
         <v>27300</v>
       </c>
       <c r="X27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Y27" s="3">
         <v>15200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>11600</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,20 +2607,23 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2700</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2569,21 +2639,21 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2594,114 +2664,120 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E33" s="3">
         <v>6700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>58800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-41700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-39900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-298300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="V33" s="3">
-        <v>27300</v>
       </c>
       <c r="W33" s="3">
         <v>27300</v>
       </c>
       <c r="X33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Y33" s="3">
         <v>15200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>11600</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E35" s="3">
         <v>6700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>58800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-41700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-39900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-298300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="V35" s="3">
-        <v>27300</v>
       </c>
       <c r="W35" s="3">
         <v>27300</v>
       </c>
       <c r="X35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Y35" s="3">
         <v>15200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>11600</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,71 +3091,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>301000</v>
+      </c>
+      <c r="E41" s="3">
         <v>448300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>423800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>524900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>533300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>672300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>794900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>762000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>761100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>757200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>728800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>730500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>845400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>941100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>912000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>894700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>990500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>968700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1075000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>126600</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3085,8 +3172,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,71 +3255,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>209400</v>
+      </c>
+      <c r="E43" s="3">
         <v>183800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>180400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>203800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>174700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>175500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>145200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>123400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>116400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>121700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>124300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>143200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>129100</v>
-      </c>
-      <c r="P43" s="3">
-        <v>126400</v>
       </c>
       <c r="Q43" s="3">
         <v>126400</v>
       </c>
       <c r="R43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="S43" s="3">
         <v>166800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>115800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>97300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>92300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>58800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3245,8 +3338,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3274,8 +3370,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3325,8 +3421,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3354,42 +3453,42 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>40900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>20200</v>
       </c>
       <c r="O45" s="3">
         <v>20200</v>
       </c>
       <c r="P45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>21300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>20400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>15000</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3405,71 +3504,74 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>540200</v>
+      </c>
+      <c r="E46" s="3">
         <v>659300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>626800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>750600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>732800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>872800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>969100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>919300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>907000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>919700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>878400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>894000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>994700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1088800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1051500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1075800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1123400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1086400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1181100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,8 +3587,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3509,13 +3614,13 @@
         <v>15000</v>
       </c>
       <c r="J47" s="3">
-        <v>17200</v>
+        <v>15000</v>
       </c>
       <c r="K47" s="3">
         <v>17200</v>
       </c>
       <c r="L47" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3565,71 +3670,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E48" s="3">
         <v>40500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>42500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>44400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>45900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>48400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>51500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>53700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>55700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>47800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>49000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>50600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>50800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>46100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35500</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,71 +3753,74 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>620700</v>
+      </c>
+      <c r="E49" s="3">
         <v>587700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>584700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>578600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>572900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>567100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>593500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>614300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>609400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>602100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>612500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>608700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>473100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>463500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>463000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>447000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>321500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>317800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>315700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>261800</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,71 +4002,74 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E52" s="3">
         <v>8500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>27300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>27200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>52000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4700</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,71 +4168,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1295300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1388100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1354800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1475400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1454000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1588800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1708000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1692100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1611500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1604600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1567100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1592000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1538300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1607600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1614400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1586900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1511000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1470100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1546800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>502400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,71 +4315,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E57" s="3">
         <v>14100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>33500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>36300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8600</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4265,8 +4396,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4274,28 +4408,28 @@
         <v>10600</v>
       </c>
       <c r="E58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F58" s="3">
         <v>9300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8900</v>
-      </c>
-      <c r="L58" s="3">
-        <v>7000</v>
       </c>
       <c r="M58" s="3">
         <v>7000</v>
@@ -4327,8 +4461,8 @@
       <c r="V58" s="3">
         <v>7000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>7000</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4345,71 +4479,74 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E59" s="3">
         <v>23300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>51600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>67100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>55800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>56600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>48400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>40100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>40900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>42200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>39100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>44400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,71 +4562,74 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E60" s="3">
         <v>123900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>114400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>102500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>116500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>122600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>117800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>82600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>69000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>76300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>85000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>79600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>81100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>72700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>65500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>63000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>59600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>60200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>60000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,71 +4645,74 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>530600</v>
+      </c>
+      <c r="E61" s="3">
         <v>532800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>535300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>695000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>698000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>696100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>701100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>704600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>707100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>651800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>652800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>653800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>654800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>655900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>656900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>657900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>658900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>659900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>688900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>689900</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4585,71 +4728,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E62" s="3">
         <v>6800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>61700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>40900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>39000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>38400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>39200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>40000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>39300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>41300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>42200</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,71 +5060,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>640900</v>
+      </c>
+      <c r="E66" s="3">
         <v>663400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>658400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>806000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>822900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>826800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>826700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>796700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>784000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>789800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>778700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>774100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>751800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>775900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>768000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>762500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>761900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>758800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>790400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>792200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5235,11 +5403,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>737000</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,71 +5506,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1430000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1441000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1447800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1451700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1458400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,71 +5838,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>654300</v>
+      </c>
+      <c r="E76" s="3">
         <v>724700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>696400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>669400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>631100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>762000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>881300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>895400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>827500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>814800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>788400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>817900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>786500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>831700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>846400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>824400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>749100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>711400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>756400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E81" s="3">
         <v>6700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>58800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-41700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-39900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-298300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="V81" s="3">
-        <v>27300</v>
       </c>
       <c r="W81" s="3">
         <v>27300</v>
       </c>
       <c r="X81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Y81" s="3">
         <v>15200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>11600</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,74 +6208,75 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E83" s="3">
         <v>-47000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-10900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4300</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,74 +6704,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E89" s="3">
         <v>44700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>86900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>42600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>60300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>32300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>31900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>51000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>49800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>48600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>34900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>45500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>14900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>32700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>38200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>45600</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,74 +6820,75 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-400</v>
       </c>
       <c r="H91" s="3">
         <v>-400</v>
       </c>
       <c r="I91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,74 +7067,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-51900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-163600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-34400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-132700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-73500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3400</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6979,8 +7213,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,74 +7513,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-104900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-172100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-161000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-125600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-21700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-91400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-111400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>992100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>27600</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7379,8 +7628,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7430,74 +7679,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-147400</v>
+      </c>
+      <c r="E102" s="3">
         <v>24600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-101100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-139000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-122600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>32900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>28400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-114900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-95700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>29100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-98700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>21800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-106300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>951300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>30800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>69800</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -656,212 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>203100</v>
+      </c>
+      <c r="E8" s="3">
         <v>203000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>198600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>195300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>197900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>196600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>180000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>189700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>184000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>184100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>187300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>191800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>203300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>213300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>195100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>176600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>160400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>153500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>140500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>123300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>133400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>113300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>101700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>91500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>81700</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -869,165 +876,171 @@
         <v>13400</v>
       </c>
       <c r="E9" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F9" s="3">
         <v>12200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16700</v>
-      </c>
-      <c r="M9" s="3">
-        <v>17400</v>
       </c>
       <c r="N9" s="3">
         <v>17400</v>
       </c>
       <c r="O9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="P9" s="3">
         <v>18000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>11300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2900</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>189700</v>
+      </c>
+      <c r="E10" s="3">
         <v>189600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>186400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>183600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>188700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>185400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>186000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>161200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>173300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>167300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>166700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>169900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>173800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>191000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>199400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>183800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>165500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>150000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>144300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>133000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>116500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>127400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>108700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>98300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>88400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>78800</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E12" s="3">
         <v>31100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>30900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>39600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>36800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>35900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>35400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>35000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>35100</v>
       </c>
       <c r="R12" s="3">
         <v>35100</v>
       </c>
       <c r="S12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="T12" s="3">
         <v>29600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>26200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>23700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>15800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5600</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,55 +1240,58 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>4400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>20400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>13000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>77000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>1800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-8500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>18700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1279,11 +1299,11 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1291,12 +1311,12 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>4900</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1306,91 +1326,97 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E15" s="3">
         <v>20900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>17500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>17000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>15900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>-3100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>33000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>15500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>10200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>8400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>4400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>5200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2600</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>176300</v>
+      </c>
+      <c r="E17" s="3">
         <v>175200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>160000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>174800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>180700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>177500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>137900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>218300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>171400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>172700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>182400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>203000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>195800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>183600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>201500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>188100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>177000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>165400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>453000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>202100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>81600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>89700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>82400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>63900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>53500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>53700</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E18" s="3">
         <v>27800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>38500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>20400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>20400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>58700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-38300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-299500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-61600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>41700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>43700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>30900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>37800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>38000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>28000</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,23 +1647,24 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>2700</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,21 +1680,21 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>5500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1671,158 +1705,164 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
       <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E21" s="3">
         <v>48700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>57600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>35300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>36800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>36300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>55700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>34400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>22400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-295000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-56500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>46300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>48100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>44000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E22" s="3">
         <v>10600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>14600</v>
       </c>
       <c r="H22" s="3">
         <v>14600</v>
       </c>
       <c r="I22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J22" s="3">
         <v>14800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>5900</v>
       </c>
       <c r="Q22" s="3">
         <v>5900</v>
@@ -1837,200 +1877,209 @@
         <v>5900</v>
       </c>
       <c r="U22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="V22" s="3">
         <v>6200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>13400</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E23" s="3">
         <v>16700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-24600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>13900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-305600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-67900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>35000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>35100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>17900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>25300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>25000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14700</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E24" s="3">
         <v>5600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-8100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-46700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-8700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>45800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-37300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-12600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-17900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3200</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E26" s="3">
         <v>11100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>58800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-41700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-39900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-298300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="W26" s="3">
-        <v>27300</v>
       </c>
       <c r="X26" s="3">
         <v>27300</v>
       </c>
       <c r="Y26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Z26" s="3">
         <v>15200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>19700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>11600</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E27" s="3">
         <v>11100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>58800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-41700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-39900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-298300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>27300</v>
       </c>
       <c r="X27" s="3">
         <v>27300</v>
       </c>
       <c r="Y27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Z27" s="3">
         <v>15200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>19700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>11600</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,23 +2677,26 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2700</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2642,21 +2712,21 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-5500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2667,117 +2737,123 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
       <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E33" s="3">
         <v>11100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>58800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-41700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-39900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-298300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="W33" s="3">
-        <v>27300</v>
       </c>
       <c r="X33" s="3">
         <v>27300</v>
       </c>
       <c r="Y33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Z33" s="3">
         <v>15200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>19700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>11600</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E35" s="3">
         <v>11100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>58800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-41700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-39900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-298300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="W35" s="3">
-        <v>27300</v>
       </c>
       <c r="X35" s="3">
         <v>27300</v>
       </c>
       <c r="Y35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Z35" s="3">
         <v>15200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>19700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>11600</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,74 +3178,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>281300</v>
+      </c>
+      <c r="E41" s="3">
         <v>301000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>448300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>423800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>524900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>533300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>672300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>794900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>762000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>761100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>757200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>728800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>730500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>845400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>941100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>912000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>894700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>990500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>968700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1075000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>126600</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,74 +3348,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>241300</v>
+      </c>
+      <c r="E43" s="3">
         <v>209400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>183800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>180400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>203800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>174700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>175500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>145200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>123400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>116400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>121700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>124300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>143200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>129100</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>126400</v>
       </c>
       <c r="R43" s="3">
         <v>126400</v>
       </c>
       <c r="S43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="T43" s="3">
         <v>166800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>115800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>97300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>92300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>58800</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3373,8 +3469,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3424,8 +3520,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3456,42 +3555,42 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>40900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25400</v>
-      </c>
-      <c r="O45" s="3">
-        <v>20200</v>
       </c>
       <c r="P45" s="3">
         <v>20200</v>
       </c>
       <c r="Q45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="R45" s="3">
         <v>21300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15000</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3507,74 +3606,77 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>550600</v>
+      </c>
+      <c r="E46" s="3">
         <v>540200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>659300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>626800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>750600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>732800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>872800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>969100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>919300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>907000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>919700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>878400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>894000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>994700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1088800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1051500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1075800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1123400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1086400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1181100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>200400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3590,8 +3692,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3617,13 +3722,13 @@
         <v>15000</v>
       </c>
       <c r="K47" s="3">
-        <v>17200</v>
+        <v>15000</v>
       </c>
       <c r="L47" s="3">
         <v>17200</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3673,74 +3778,77 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E48" s="3">
         <v>34400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>42500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>44400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>48400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>53700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>51400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>47800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>50600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>50800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>46100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35500</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3756,74 +3864,77 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>625600</v>
+      </c>
+      <c r="E49" s="3">
         <v>620700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>587700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>584700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>578600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>572900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>567100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>593500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>614300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>609400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>602100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>612500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>608700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>473100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>463500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>463000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>447000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>321500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>317800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>315700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>261800</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,74 +4122,77 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E52" s="3">
         <v>7800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>27200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>38000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>20900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>52000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>15200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4700</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,74 +4294,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1318700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1295300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1388100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1354800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1475400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1454000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1588800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1708000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1692100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1611500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1604600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1567100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1592000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1538300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1607600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1614400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1586900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1511000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1470100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1546800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>502400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,74 +4446,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E57" s="3">
         <v>15300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>36300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4399,40 +4530,43 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10600</v>
+        <v>9800</v>
       </c>
       <c r="E58" s="3">
         <v>10600</v>
       </c>
       <c r="F58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G58" s="3">
         <v>9300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>15000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8900</v>
-      </c>
-      <c r="M58" s="3">
-        <v>7000</v>
       </c>
       <c r="N58" s="3">
         <v>7000</v>
@@ -4464,8 +4598,8 @@
       <c r="W58" s="3">
         <v>7000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>7000</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -4482,74 +4616,77 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E59" s="3">
         <v>20300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>51600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>67100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>55800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>39500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>56600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>48400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>40100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>40900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>42200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>39100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>44400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4565,74 +4702,77 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E60" s="3">
         <v>103400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>123900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>114400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>102500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>116500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>122600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>117800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>82600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>69000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>76300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>85000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>79600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>59400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>81100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>72700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>65500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>63000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>59600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>60200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>60000</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4648,74 +4788,77 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>537700</v>
+      </c>
+      <c r="E61" s="3">
         <v>530600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>532800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>535300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>695000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>698000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>696100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>701100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>704600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>707100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>651800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>652800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>653800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>654800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>655900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>656900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>657900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>658900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>659900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>688900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>689900</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4731,74 +4874,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E62" s="3">
         <v>6900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>61700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>40600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>37600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>39000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>38400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>39200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>40000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>39300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>41300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>42200</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,74 +5218,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>675700</v>
+      </c>
+      <c r="E66" s="3">
         <v>640900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>663400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>658400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>806000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>822900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>826800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>826700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>796700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>784000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>789800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>778700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>774100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>751800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>775900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>768000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>762500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>761900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>758800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>790400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>792200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5406,11 +5574,11 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>737000</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,74 +5680,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1417100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1430000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1441000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1447800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1451700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1458400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,74 +6024,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>643000</v>
+      </c>
+      <c r="E76" s="3">
         <v>654300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>724700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>696400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>669400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>631100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>762000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>881300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>895400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>827500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>814800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>788400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>817900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>786500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>831700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>846400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>824400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>749100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>711400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>756400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E81" s="3">
         <v>11100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>58800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-41700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-39900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-298300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="W81" s="3">
-        <v>27300</v>
       </c>
       <c r="X81" s="3">
         <v>27300</v>
       </c>
       <c r="Y81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="Z81" s="3">
         <v>15200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>19700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>11600</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,77 +6407,78 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E83" s="3">
         <v>15900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-47000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-10900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>15500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4300</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,77 +6921,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E89" s="3">
         <v>9400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>44700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>86900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>42600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>60300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>31900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>33700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>51000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>30100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>49800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>48600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>34900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>45500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>38200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>45600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,77 +7041,78 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-400</v>
       </c>
       <c r="I91" s="3">
         <v>-400</v>
       </c>
       <c r="J91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,77 +7297,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-51900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-163600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-34400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-132700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-73500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7216,8 +7450,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,77 +7759,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-50900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-104900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-172100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-161000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-125600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-21700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-91400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-11500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-14000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-111400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>992100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>27600</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,8 +7880,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7682,77 +7931,80 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-147400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-101100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-139000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-122600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>32900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>28400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-114900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-95700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>29100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-98700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>21800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-106300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>951300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>30800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>69800</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7763,6 +8015,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -656,231 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>194800</v>
+      </c>
+      <c r="E8" s="3">
         <v>196000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>203100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>203000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>198600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>195300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>197900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>196600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>180000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>189700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>184000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>184100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>187300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>191800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>203300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>213300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>195100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>176600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>160400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>153500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>140500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>123300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>133400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>113300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>101700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>91500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>81700</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>13400</v>
+        <v>17500</v>
       </c>
       <c r="E9" s="3">
         <v>13400</v>
@@ -889,171 +895,177 @@
         <v>13400</v>
       </c>
       <c r="G9" s="3">
+        <v>13400</v>
+      </c>
+      <c r="H9" s="3">
         <v>12200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16700</v>
-      </c>
-      <c r="O9" s="3">
-        <v>17400</v>
       </c>
       <c r="P9" s="3">
         <v>17400</v>
       </c>
       <c r="Q9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="R9" s="3">
         <v>18000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>11300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2900</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>177300</v>
+      </c>
+      <c r="E10" s="3">
         <v>182600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>189700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>189600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>186400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>183600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>188700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>185400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>186000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>161200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>173300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>167300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>166700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>169900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>173800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>191000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>199400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>183800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>165500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>150000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>144300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>133000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>116500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>127400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>108700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>98300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>88400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>78800</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E12" s="3">
         <v>31000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>29900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>39600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>32900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>36800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>35900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>35400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>35000</v>
-      </c>
-      <c r="S12" s="3">
-        <v>35100</v>
       </c>
       <c r="T12" s="3">
         <v>35100</v>
       </c>
       <c r="U12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="V12" s="3">
         <v>29600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>26200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>23700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>15800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>12000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>5600</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,61 +1279,64 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>14300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>4400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>20400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>13000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>77000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-8500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>18700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1325,11 +1344,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
@@ -1337,12 +1356,12 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="3">
         <v>4900</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,97 +1371,103 @@
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E15" s="3">
         <v>21400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>20900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-3100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>33000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>15500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>14000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>13300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>11400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>10600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>10200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>5400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>5200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2600</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>157800</v>
+      </c>
+      <c r="E17" s="3">
         <v>181400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>176300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>175200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>160000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>174800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>180700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>177500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>137900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>218300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>171400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>172700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>182400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>203000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>195800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>183600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>201500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>188100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>177000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>165400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>453000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>202100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>81600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>89700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>82400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>63900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>53500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>53700</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E18" s="3">
         <v>14600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>26800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>27800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>38500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>20400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>58700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-38300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-299500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-61600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>41700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>43700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>30900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>37800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>38000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>28000</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,29 +1714,30 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1720,21 +1753,21 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>5500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1745,170 +1778,176 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
       </c>
       <c r="AA20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E21" s="3">
         <v>36100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>48700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>57600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>35300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>36800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>36300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>34400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>22700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>10100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>31200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>8000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-295000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-56500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>46300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>48100</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3">
         <v>44000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E22" s="3">
         <v>10800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>14600</v>
       </c>
       <c r="J22" s="3">
         <v>14600</v>
       </c>
       <c r="K22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="L22" s="3">
         <v>14800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>5900</v>
       </c>
       <c r="S22" s="3">
         <v>5900</v>
@@ -1923,212 +1962,221 @@
         <v>5900</v>
       </c>
       <c r="W22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="X22" s="3">
         <v>6200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>6300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>6800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>13300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>13400</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E23" s="3">
         <v>6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-24600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-305600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-67900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>35000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>35100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>17900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>25300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>25000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>14700</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-8100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-46700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>19500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-8700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>45800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>19200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-37300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-12600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-7400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3200</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>58800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-39900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-298300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>27300</v>
       </c>
       <c r="Z26" s="3">
         <v>27300</v>
       </c>
       <c r="AA26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AB26" s="3">
         <v>15200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>11600</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>58800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>12300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-39900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>31100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-298300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>27300</v>
       </c>
       <c r="Z27" s="3">
         <v>27300</v>
       </c>
       <c r="AA27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AB27" s="3">
         <v>15200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>19600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11600</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,29 +2816,32 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2788,21 +2857,21 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>-5500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2813,123 +2882,129 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E33" s="3">
         <v>1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>58800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>12300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-39900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>31100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-298300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>27300</v>
       </c>
       <c r="Z33" s="3">
         <v>27300</v>
       </c>
       <c r="AA33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AB33" s="3">
         <v>15200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11600</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E35" s="3">
         <v>1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>58800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>12300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-39900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>31100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-298300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>27300</v>
       </c>
       <c r="Z35" s="3">
         <v>27300</v>
       </c>
       <c r="AA35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AB35" s="3">
         <v>15200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11600</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,80 +3351,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>261800</v>
+      </c>
+      <c r="E41" s="3">
         <v>273500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>281300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>301000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>448300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>423800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>524900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>533300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>672300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>794900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>762000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>761100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>757200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>728800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>730500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>845400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>941100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>912000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>894700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>990500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>968700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1075000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>126600</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3355,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,80 +3533,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>254900</v>
+      </c>
+      <c r="E43" s="3">
         <v>270900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>241300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>209400</v>
       </c>
-      <c r="G43" s="3">
-        <v>183800</v>
-      </c>
       <c r="H43" s="3">
+        <v>160800</v>
+      </c>
+      <c r="I43" s="3">
         <v>180400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>203800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>174700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>175500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>145200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>123400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>116400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>121700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>124300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>143200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>129100</v>
-      </c>
-      <c r="S43" s="3">
-        <v>126400</v>
       </c>
       <c r="T43" s="3">
         <v>126400</v>
       </c>
       <c r="U43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="V43" s="3">
         <v>166800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>115800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>97300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>92300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>58800</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3533,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3571,8 +3666,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3622,13 +3717,16 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>98300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -3639,8 +3737,8 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>22900</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -3660,42 +3758,42 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>40900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>20200</v>
       </c>
       <c r="R45" s="3">
         <v>20200</v>
       </c>
       <c r="S45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="T45" s="3">
         <v>21300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>14200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>15000</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,80 +3809,83 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>643100</v>
+      </c>
+      <c r="E46" s="3">
         <v>565500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>550600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>540200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>659300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>626800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>750600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>732800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>872800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>969100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>919300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>907000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>919700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>878400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>894000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>994700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1088800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1051500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1075800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1123400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1086400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1181100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>200400</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3800,8 +3901,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3833,13 +3937,13 @@
         <v>15000</v>
       </c>
       <c r="M47" s="3">
-        <v>17200</v>
+        <v>15000</v>
       </c>
       <c r="N47" s="3">
         <v>17200</v>
       </c>
       <c r="O47" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3889,80 +3993,83 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E48" s="3">
         <v>41000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>42500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>45900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>48400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>53700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>55700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>51400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>49500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>47800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>49000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>50600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>50800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>46100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35500</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3978,80 +4085,83 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>633700</v>
+      </c>
+      <c r="E49" s="3">
         <v>626600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>625600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>620700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>587700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>584700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>578600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>572900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>567100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>593500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>614300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>609400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>602100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>612500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>608700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>473100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>463500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>463000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>447000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>321500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>317800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>315700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>261800</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,80 +4361,83 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E52" s="3">
         <v>8300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>27300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>24200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>27200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>38000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>20900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>52000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4700</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4334,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,80 +4545,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1404100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1325500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1318700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1295300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1388100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1354800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1475400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1454000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1588800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1708000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1692100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1611500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1604600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1567100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1592000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1538300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1607600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1614400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1586900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1511000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1470100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1546800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>502400</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4512,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,80 +4707,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E57" s="3">
         <v>28700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>32900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>18400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8600</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4667,8 +4797,11 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4679,34 +4812,34 @@
         <v>9800</v>
       </c>
       <c r="F58" s="3">
-        <v>10600</v>
+        <v>9800</v>
       </c>
       <c r="G58" s="3">
         <v>10600</v>
       </c>
       <c r="H58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I58" s="3">
         <v>9300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8900</v>
-      </c>
-      <c r="O58" s="3">
-        <v>7000</v>
       </c>
       <c r="P58" s="3">
         <v>7000</v>
@@ -4738,8 +4871,8 @@
       <c r="Y58" s="3">
         <v>7000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
+      <c r="Z58" s="3">
+        <v>7000</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
@@ -4756,80 +4889,83 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E59" s="3">
         <v>56300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>23300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>51600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>67100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>55800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>39500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>56600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>48400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>40100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>40900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>42200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>39100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>44400</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4845,80 +4981,83 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E60" s="3">
         <v>181900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>130900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>103400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>123900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>114400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>102500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>116500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>122600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>117800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>82600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>69000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>76300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>85000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>79600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>59400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>81100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>72700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>65500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>63000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>59600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>60200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>60000</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4934,80 +5073,83 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>533100</v>
+      </c>
+      <c r="E61" s="3">
         <v>535400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>537700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>530600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>532800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>535300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>695000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>698000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>696100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>701100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>704600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>707100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>651800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>652800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>653800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>654800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>655900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>656900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>657900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>658900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>659900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>688900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>689900</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5023,80 +5165,83 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E62" s="3">
         <v>7600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>61700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>40900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>40600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>37600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>39000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>38400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>39200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>40000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>39300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>41300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>42200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5112,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,80 +5533,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>787800</v>
+      </c>
+      <c r="E66" s="3">
         <v>724800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>675700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>640900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>663400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>658400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>806000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>822900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>826800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>826700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>796700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>784000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>789800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>778700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>774100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>751800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>775900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>768000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>762500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>761900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>758800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>790400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>792200</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5748,11 +5915,11 @@
         <v>0</v>
       </c>
       <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>737000</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
       <c r="AA70" s="3">
         <v>0</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,80 +6027,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1410600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1416000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1417100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1430000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1441000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1447800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1451700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1458400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5946,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,80 +6395,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>616300</v>
+      </c>
+      <c r="E76" s="3">
         <v>600700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>643000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>654300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>724700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>696400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>669400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>631100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>762000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>881300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>895400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>827500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>814800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>788400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>817900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>786500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>831700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>846400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>824400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>749100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>711400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>756400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6302,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E81" s="3">
         <v>1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>58800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-41700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>12300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-39900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>31100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-298300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>27300</v>
       </c>
       <c r="Z81" s="3">
         <v>27300</v>
       </c>
       <c r="AA81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AB81" s="3">
         <v>15200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11600</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,83 +6804,84 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="E83" s="3">
         <v>17500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-47000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>33000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-10900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>15500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4300</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6696,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,83 +7354,86 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E89" s="3">
         <v>76000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>49600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>44700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>86900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>42600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>60300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>29900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>33700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>51000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>30100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>49800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>48600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>34900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>45500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>14900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>32700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>38200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>45600</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7230,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,83 +7482,84 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>-400</v>
       </c>
       <c r="L91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-700</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7352,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,83 +7756,86 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-51900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-163600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-34400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-132700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-73500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7619,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7690,8 +7923,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,83 +8250,86 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-65800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-50900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-104900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-172100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-161000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-125600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-91400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-14000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-111400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>992100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>27600</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8097,8 +8342,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8135,8 +8383,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8186,83 +8434,86 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-147400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>24600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-101100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-139000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-122600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>32900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>28400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-114900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-95700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>29100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>17300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-98700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>21800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-106300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>951300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>30800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>69800</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8273,6 +8524,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GDRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -656,240 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E8" s="3">
         <v>194800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>196000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>203100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>203000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>198600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>195300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>197900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>196600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>180000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>189700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>184000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>184100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>187300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>191800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>203300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>213300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>195100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>176600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>160400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>153500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>140500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>123300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>133400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>113300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>101700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>91500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>81700</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E9" s="3">
         <v>17500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>13400</v>
       </c>
       <c r="F9" s="3">
         <v>13400</v>
@@ -898,174 +905,180 @@
         <v>13400</v>
       </c>
       <c r="H9" s="3">
+        <v>13400</v>
+      </c>
+      <c r="I9" s="3">
         <v>12200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16700</v>
-      </c>
-      <c r="P9" s="3">
-        <v>17400</v>
       </c>
       <c r="Q9" s="3">
         <v>17400</v>
       </c>
       <c r="R9" s="3">
+        <v>17400</v>
+      </c>
+      <c r="S9" s="3">
         <v>18000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2900</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>173900</v>
+      </c>
+      <c r="E10" s="3">
         <v>177300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>182600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>189700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>189600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>186400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>183600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>188700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>185400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>186000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>161200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>173300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>167300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>166700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>169900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>173800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>191000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>199400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>183800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>165500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>150000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>144300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>133000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>116500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>127400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>108700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>98300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>88400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>78800</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E12" s="3">
         <v>25200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>29900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>31000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>39600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>31300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>32900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>36800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>35900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>35400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>35000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>35100</v>
       </c>
       <c r="U12" s="3">
         <v>35100</v>
       </c>
       <c r="V12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="W12" s="3">
         <v>29600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>26200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>23700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>15800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>12000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5600</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,64 +1299,67 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>14300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>4400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>20400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>13000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>77000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>18700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1347,11 +1367,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1359,12 +1379,12 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="3">
         <v>4900</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1374,100 +1394,106 @@
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E15" s="3">
         <v>23100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>21400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>15900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-3100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>33000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>14900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>15500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>14000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>13300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>11400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>10600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>10200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>8400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>5400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>3100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2600</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E17" s="3">
         <v>157800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>181400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>176300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>175200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>160000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>174800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>180700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>137900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>218300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>171400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>172700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>182400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>203000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>195800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>183600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>201500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>188100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>177000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>165400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>453000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>202100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>81600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>89700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>82400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>63900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>53500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>53700</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E18" s="3">
         <v>37000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>14600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>58700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-38300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-15700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>19700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>11800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-299500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-61600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>41700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>43700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>30900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>37800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>38000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>28000</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,32 +1748,33 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1756,21 +1790,21 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>5500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1781,176 +1815,182 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
       </c>
       <c r="AB20" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E21" s="3">
         <v>60100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>36100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>47200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>48700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>57600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>35300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>36800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>36300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>34400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-295000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-56500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>46300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>48100</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3">
         <v>44000</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E22" s="3">
         <v>10400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>14600</v>
       </c>
       <c r="K22" s="3">
         <v>14600</v>
       </c>
       <c r="L22" s="3">
+        <v>14600</v>
+      </c>
+      <c r="M22" s="3">
         <v>14800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>5900</v>
       </c>
       <c r="T22" s="3">
         <v>5900</v>
@@ -1965,218 +2005,227 @@
         <v>5900</v>
       </c>
       <c r="X22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Y22" s="3">
         <v>6200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>6300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>6800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>13300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>13400</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E23" s="3">
         <v>14200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>19600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>16700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>11400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-24600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-22300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>13900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-305600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-67900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>35000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>35100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>17900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>25300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>25000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>14700</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E24" s="3">
         <v>8800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-8100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-46700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-8700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>45800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>19200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-37300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-12600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3200</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-38500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>58800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-41700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>12300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-39900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-18100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>31100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-298300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>27300</v>
       </c>
       <c r="AA26" s="3">
         <v>27300</v>
       </c>
       <c r="AB26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AC26" s="3">
         <v>15200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>19700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>11600</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>5400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-38500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>58800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-41700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-39900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-18100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>31100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-298300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>27300</v>
       </c>
       <c r="AA27" s="3">
         <v>27300</v>
       </c>
       <c r="AB27" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AC27" s="3">
         <v>15200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>19700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>11600</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2696,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,32 +2886,35 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,21 +2930,21 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2885,126 +2955,132 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
       <c r="AB32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC32" s="3">
         <v>2900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>5400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-38500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>58800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-41700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>12300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-39900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-18100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>31100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-298300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>27300</v>
       </c>
       <c r="AA33" s="3">
         <v>27300</v>
       </c>
       <c r="AB33" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AC33" s="3">
         <v>15200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>19700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11600</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>5400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-38500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>58800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-41700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>12300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-39900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-18100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>31100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-298300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>27300</v>
       </c>
       <c r="AA35" s="3">
         <v>27300</v>
       </c>
       <c r="AB35" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AC35" s="3">
         <v>15200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>19700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11600</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,83 +3438,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>235700</v>
+      </c>
+      <c r="E41" s="3">
         <v>261800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>273500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>281300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>301000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>448300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>423800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>524900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>533300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>672300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>794900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>762000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>761100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>757200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>728800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>730500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>845400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>941100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>912000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>894700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>990500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>968700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1075000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>126600</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,8 +3531,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,83 +3626,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>244600</v>
+      </c>
+      <c r="E43" s="3">
         <v>254900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>270900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>241300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>209400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>160800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>180400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>203800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>174700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>175500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>145200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>123400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>116400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>121700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>124300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>143200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>129100</v>
-      </c>
-      <c r="T43" s="3">
-        <v>126400</v>
       </c>
       <c r="U43" s="3">
         <v>126400</v>
       </c>
       <c r="V43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="W43" s="3">
         <v>166800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>115800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>97300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>92300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>58800</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3628,8 +3721,11 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3669,8 +3765,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3720,29 +3816,32 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>753500</v>
+      </c>
+      <c r="E45" s="3">
         <v>98300</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>22900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3761,42 +3860,42 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>40900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>25400</v>
-      </c>
-      <c r="R45" s="3">
-        <v>20200</v>
       </c>
       <c r="S45" s="3">
         <v>20200</v>
       </c>
       <c r="T45" s="3">
+        <v>20200</v>
+      </c>
+      <c r="U45" s="3">
         <v>21300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>20400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>13800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>15000</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3812,83 +3911,86 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1266500</v>
+      </c>
+      <c r="E46" s="3">
         <v>643100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>565500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>550600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>540200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>659300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>626800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>750600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>732800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>872800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>969100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>919300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>907000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>919700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>878400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>894000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>994700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1088800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1051500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1075800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1123400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1086400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1181100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>200400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3904,8 +4006,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3940,13 +4045,13 @@
         <v>15000</v>
       </c>
       <c r="N47" s="3">
-        <v>17200</v>
+        <v>15000</v>
       </c>
       <c r="O47" s="3">
         <v>17200</v>
       </c>
       <c r="P47" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3996,83 +4101,86 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E48" s="3">
         <v>41100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>42500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>45900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>48400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>53700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>55700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>51400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>49300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>47800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>49000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>50600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>50800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>46100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>35500</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4088,83 +4196,86 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>631700</v>
+      </c>
+      <c r="E49" s="3">
         <v>633700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>626600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>625600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>620700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>587700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>584700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>578600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>572900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>567100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>593500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>614300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>609400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>602100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>612500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>608700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>473100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>463500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>463000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>447000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>321500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>317800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>315700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>261800</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4291,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,83 +4481,86 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E52" s="3">
         <v>14100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>27300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>27200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>38000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>20900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>52000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>15500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>15100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4700</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4456,8 +4576,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,83 +4671,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2021300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1404100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1325500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1318700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1295300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1388100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1354800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1475400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1454000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1588800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1708000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1692100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1611500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1604600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1567100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1592000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1538300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1607600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1614400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1586900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1511000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1470100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1546800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>502400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4640,8 +4766,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,83 +4838,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E57" s="3">
         <v>19400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>36300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>32900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4800,13 +4931,16 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9800</v>
+        <v>10000</v>
       </c>
       <c r="E58" s="3">
         <v>9800</v>
@@ -4815,34 +4949,34 @@
         <v>9800</v>
       </c>
       <c r="G58" s="3">
-        <v>10600</v>
+        <v>9800</v>
       </c>
       <c r="H58" s="3">
         <v>10600</v>
       </c>
       <c r="I58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="J58" s="3">
         <v>9300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8900</v>
-      </c>
-      <c r="P58" s="3">
-        <v>7000</v>
       </c>
       <c r="Q58" s="3">
         <v>7000</v>
@@ -4874,8 +5008,8 @@
       <c r="Z58" s="3">
         <v>7000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
+      <c r="AA58" s="3">
+        <v>7000</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
@@ -4892,83 +5026,86 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>759600</v>
+      </c>
+      <c r="E59" s="3">
         <v>136800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>56300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>23300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>51600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>67100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>55800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>39500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>56600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>40100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>40900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>42200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>39100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>44400</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,83 +5121,86 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>859200</v>
+      </c>
+      <c r="E60" s="3">
         <v>246000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>181900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>130900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>103400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>123900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>114400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>102500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>116500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>122600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>117800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>82600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>69000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>76300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>85000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>79600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>59400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>81100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>72700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>65500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>63000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>59600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>60200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>60000</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5076,83 +5216,86 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>531400</v>
+      </c>
+      <c r="E61" s="3">
         <v>533100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>535400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>537700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>530600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>532800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>535300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>695000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>698000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>696100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>701100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>704600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>707100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>651800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>652800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>653800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>654800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>655900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>656900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>657900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>658900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>659900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>688900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>689900</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5168,8 +5311,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5177,74 +5323,74 @@
         <v>8700</v>
       </c>
       <c r="E62" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F62" s="3">
         <v>7600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>61700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>40900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>40600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>37600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>39000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>38400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>39200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>40000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>39300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>41300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>42200</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5260,8 +5406,11 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,83 +5691,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1399300</v>
+      </c>
+      <c r="E66" s="3">
         <v>787800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>724800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>675700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>640900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>663400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>658400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>806000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>822900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>826800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>826700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>796700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>784000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>789800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>778700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>774100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>751800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>775900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>768000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>762500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>761900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>758800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>790400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>792200</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5628,8 +5786,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5918,11 +6086,11 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
         <v>737000</v>
       </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,83 +6201,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1409400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1410600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1416000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1417100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1430000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1441000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1447800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1451700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1458400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1431500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1393000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1451800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1446600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1404800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1403400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1375800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1357700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1388800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-1092200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6122,8 +6296,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,83 +6581,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>622000</v>
+      </c>
+      <c r="E76" s="3">
         <v>616300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>600700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>643000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>654300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>724700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>696400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>669400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>631100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>762000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>881300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>895400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>827500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>814800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>788400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>817900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>786500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>831700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>846400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>824400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>749100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>711400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>756400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1026700</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6490,8 +6676,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>5400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-38500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>58800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-41700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>12300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-39900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-18100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>31100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-298300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-50000</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>27300</v>
       </c>
       <c r="AA81" s="3">
         <v>27300</v>
       </c>
       <c r="AB81" s="3">
+        <v>27300</v>
+      </c>
+      <c r="AC81" s="3">
         <v>15200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>19700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11600</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,86 +7003,87 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E83" s="3">
         <v>-37100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>17000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-47000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>33000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-10900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>15500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>14000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4300</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6897,8 +7096,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,86 +7571,89 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E89" s="3">
         <v>32900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>76000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>49600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>44700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>86900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>42600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>60300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>29900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>32300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>31900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>33700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>51000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>30100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>49800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>48600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>34900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>45500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>14900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>32700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>38200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>45600</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7449,8 +7666,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,86 +7703,87 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-400</v>
       </c>
       <c r="L91" s="3">
         <v>-400</v>
       </c>
       <c r="M91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-700</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7575,8 +7796,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,86 +7986,89 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-18000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-18300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-51900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-163600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-34400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-27100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-132700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-73500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7851,8 +8081,11 @@
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7926,8 +8160,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7977,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,86 +8496,89 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-65800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-50900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-104900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-172100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-161000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-125600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-14000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-21700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-91400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-14000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-111400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>992100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>27600</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8345,8 +8591,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8386,8 +8635,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8437,86 +8686,89 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-147400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-101100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-139000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-122600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>32900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>28400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-114900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-95700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>29100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>17300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-98700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>21800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-106300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>951300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>30800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>69800</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8527,6 +8779,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
